--- a/output/remote_jobs.xlsx
+++ b/output/remote_jobs.xlsx
@@ -479,7 +479,11 @@
           <t>accountant, support, accounting, payroll, financial, sales, health, healthcare, non tech</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>2026-03-05T19:00:05+00:00</t>
@@ -517,7 +521,11 @@
           <t>python, game, technical, support, code, math, node, lead</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-03-09T22:00:13+00:00</t>
@@ -555,7 +563,11 @@
           <t>game, design, designer, mobile, strategy, content, senior, junior, digital nomad</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-02-28T21:00:14+00:00</t>
@@ -593,7 +605,11 @@
           <t>director, students, training, support, software</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-03-10T06:00:23+00:00</t>
@@ -631,7 +647,11 @@
           <t>architect, design, security, training, technical, growth, serverless, cloud, management, lead, junior, health, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-03-03T21:00:19+00:00</t>
@@ -669,7 +689,11 @@
           <t>design, security, training, architect, technical, support, cloud, node, management, operational, health, engineer, digital nomad</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-03-07T20:00:08+00:00</t>
@@ -707,7 +731,11 @@
           <t>design, crypto, security, support, financial, investment, api, lead, operations, operational, digital nomad</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-03-09T07:00:07+00:00</t>
@@ -745,7 +773,11 @@
           <t>analyst, crypto, training, support, financial, investment, fintech, api, operations, sales, non tech</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-03-05T11:00:07+00:00</t>
@@ -825,7 +857,11 @@
           <t>manager, technical, software, cloud, operational, engineering</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-03-07T13:00:12+00:00</t>
@@ -863,7 +899,11 @@
           <t>design, game, technical, developer, animator, animation, content, senior, digital nomad</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-03-03T21:00:06+00:00</t>
@@ -901,7 +941,11 @@
           <t>assistant, design, support, admin, content, sales, executive, full-time, digital nomad</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-03-03T07:00:02+00:00</t>
@@ -939,7 +983,11 @@
           <t>support, operational, analytics, engineering</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-03-07T00:00:35+00:00</t>
@@ -977,7 +1025,11 @@
           <t>developer, back-end, python, reliability, backend, ecommerce, e-commerce, digital nomad</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-03-06T02:00:12+00:00</t>
@@ -1057,7 +1109,11 @@
           <t>design, designer, growth, web, marketing, go, health, digital nomad</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-03-10T10:00:06+00:00</t>
@@ -1097,7 +1153,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>6000-0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1137,7 +1193,11 @@
           <t>design, system, technical, support, growth, director, lead, senior, engineer, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-03-05T23:00:14+00:00</t>
@@ -1175,7 +1235,11 @@
           <t>manager, web3, security, technical, support, travel, lead, sales, full-time</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>2026-03-05T15:00:04+00:00</t>
@@ -1213,7 +1277,11 @@
           <t>teach, technical, support, code, engineer, engineering</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>2026-03-03T17:00:17+00:00</t>
@@ -1251,7 +1319,11 @@
           <t>design, ansible, security, python, training, support, growth, code, voice, devops, education, banking, mobile, management, senior, sales, go, health, recruiting, engineer, engineering, recruitment, linux, e-commerce, digital nomad</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>2026-03-07T00:01:33+00:00</t>
@@ -1289,7 +1361,11 @@
           <t>manager, design, saas, training, support, growth, director, voice, education, banking, mobile, strategy, lead, senior, operations, marketing, sales, go, health, recruiting, recruitment, executive, digital nomad</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>2026-03-04T00:01:20+00:00</t>
@@ -1327,7 +1403,11 @@
           <t>security, software, growth, video, analytics</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>2026-03-04T00:01:42+00:00</t>
@@ -1365,7 +1445,11 @@
           <t>design, saas, technical, support, growth, strategy, management, operations, operational, digital nomad</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>2026-03-09T17:00:06+00:00</t>
@@ -1403,7 +1487,11 @@
           <t>manager, crypto, cryptocurrency, api, operational, marketing, sales</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>2026-03-03T18:00:01+00:00</t>
@@ -1441,7 +1529,11 @@
           <t>analyst, embedded, security, training, consultancy, management, senior, executive</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>2026-03-04T00:00:42+00:00</t>
@@ -1479,7 +1571,11 @@
           <t>react, software, design, jira, front-end, back-end, security, training, test, code, web, javascript, html, senior, engineer, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>2026-03-05T16:00:14+00:00</t>
@@ -1517,7 +1613,11 @@
           <t>support, software, devops, cloud, lead, content, reliability, engineer, engineering</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>2026-03-07T20:00:19+00:00</t>
@@ -1555,7 +1655,11 @@
           <t>financial, fintech, banking, senior, engineer</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>2026-03-04T08:00:21+00:00</t>
@@ -1635,7 +1739,11 @@
           <t>senior, sales, engineer</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>2026-03-10T00:01:04+00:00</t>
@@ -1673,7 +1781,11 @@
           <t>vfx, technical, lead, engineering</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>2026-03-03T22:00:12+00:00</t>
@@ -1711,7 +1823,11 @@
           <t>unity, designer, senior</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>2026-03-03T22:00:26+00:00</t>
@@ -1749,7 +1865,11 @@
           <t>growth, design, frontend, architect, technical, web, mobile, leader, lead, executive, digital nomad</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>2026-03-04T00:01:31+00:00</t>
@@ -1787,7 +1907,11 @@
           <t>manager, system, technical, software, ui, code, engineering</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>2026-03-03T00:01:09+00:00</t>
@@ -1825,7 +1949,11 @@
           <t>security, design, api, engineer, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>2026-03-09T08:00:05+00:00</t>
@@ -1863,7 +1991,11 @@
           <t>support, software, senior, engineer, engineering</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>2026-03-03T16:00:17+00:00</t>
@@ -1901,7 +2033,11 @@
           <t>support, financial, finance, fintech, strategy, operations, non tech</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>2026-03-04T00:00:08+00:00</t>
@@ -1939,7 +2075,11 @@
           <t>manager, hr, training, growth, management, lead, senior, operations, reliability</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:53+00:00</t>
@@ -1977,7 +2117,11 @@
           <t>python, django, software, design, saas, security, full-stack, technical, developer, testing, code, devops, cloud, git, postgresql, senior, operations, engineer, digital nomad</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>2026-03-09T18:00:23+00:00</t>
@@ -2015,7 +2159,11 @@
           <t>web3, cryptocurrency, voice, lead, content, operations, executive</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>2026-03-09T12:00:02+00:00</t>
@@ -2053,7 +2201,11 @@
           <t>salesforce, technical, support, administrator, management, reliability, health</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>2026-03-03T18:00:12+00:00</t>
@@ -2091,7 +2243,11 @@
           <t>system, teaching, students, technical</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>2026-03-10T00:01:14+00:00</t>
@@ -2129,7 +2285,11 @@
           <t>analyst, support, testing, leader, senior, health, healthcare, non tech</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>2026-03-10T00:00:49+00:00</t>
@@ -2167,7 +2327,11 @@
           <t>design, lead, digital nomad</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>2026-03-10T00:00:18+00:00</t>
@@ -2205,7 +2369,11 @@
           <t>accountant, saas, manager, accounting, financial, go</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>2026-03-05T20:00:07+00:00</t>
@@ -2243,7 +2411,11 @@
           <t>training, support, education, admin, management, content, non tech</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>2026-03-09T08:00:03+00:00</t>
@@ -2277,7 +2449,11 @@
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>2026-03-04T16:00:04+00:00</t>
@@ -2315,7 +2491,11 @@
           <t>analyst, support, financial, senior, analytics, health, non tech</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>2026-03-07T00:00:56+00:00</t>
@@ -2353,7 +2533,11 @@
           <t>manager, design, system, architect, technical, support, growth, voice, lead, medical, health, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>2026-03-07T00:00:08+00:00</t>
@@ -2391,7 +2575,11 @@
           <t>manager, design, saas, support, growth, financial, investment, investor, fintech, strategy, management, senior, operational, analytics, sales, reliability, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:13+00:00</t>
@@ -2429,7 +2617,11 @@
           <t>design, full-stack, architect, testing, operational, engineer, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>2026-03-10T00:00:27+00:00</t>
@@ -2467,7 +2659,11 @@
           <t>manager, saas, security, technical, growth, voice, bank, management, lead, android, sales, recruitment, executive</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>2026-03-03T08:00:20+00:00</t>
@@ -2505,7 +2701,11 @@
           <t>manager, copywriting, growth, strategy, management, content, junior</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>2026-03-06T08:00:04+00:00</t>
@@ -2543,7 +2743,11 @@
           <t>full-stack, devops, financial, fintech, cloud, senior, engineer</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>2026-03-04T00:00:17+00:00</t>
@@ -2623,7 +2827,11 @@
           <t>system, security, software, devops, operations, operational, engineer, linux</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>2026-03-04T17:00:05+00:00</t>
@@ -2661,7 +2869,11 @@
           <t>embedded, growth, analytics, engineer, engineering</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>2026-03-03T16:00:07+00:00</t>
@@ -2699,7 +2911,11 @@
           <t>design, embedded, teach, students, designer, financial, banking, senior, internship, digital nomad</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>2026-03-03T12:00:05+00:00</t>
@@ -2737,7 +2953,11 @@
           <t>system, coordinator, support, management, operational, medical, health, healthcare</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>2026-03-07T00:00:20+00:00</t>
@@ -2775,7 +2995,11 @@
           <t>training, support, leader, content, health, non tech</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>2026-03-07T00:01:21+00:00</t>
@@ -2813,7 +3037,11 @@
           <t>game, design, designer, technical, lead, content, senior, digital nomad</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>2026-02-28T21:00:04+00:00</t>
@@ -2851,7 +3079,11 @@
           <t>manager, embedded, growth, director, senior, operational, medical, health</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>2026-03-10T00:00:42+00:00</t>
@@ -2889,7 +3121,11 @@
           <t>software, design, technical, leader, senior, medical, health, engineer, digital nomad</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>2026-03-10T16:00:07+00:00</t>
@@ -2927,7 +3163,11 @@
           <t>director, training, consult, support, growth, travel, voice, financial, c, leader, strategy, management, lead, senior, marketing, sales, health, recruitment, executive, full-time</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>2026-03-10T00:00:56+00:00</t>
@@ -2965,7 +3205,11 @@
           <t>director, financial, management, sales</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>2026-03-03T08:00:13+00:00</t>
@@ -3003,7 +3247,11 @@
           <t>manager, financial, management, sales, non tech</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>2026-03-04T00:01:12+00:00</t>
@@ -3041,7 +3289,11 @@
           <t>director, saas, system, growth, leader, strategy, lead, sales, medical, health</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:31+00:00</t>
@@ -3079,7 +3331,11 @@
           <t>technical, growth, strategy, lead, senior, health, engineering</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>2026-03-09T18:00:06+00:00</t>
@@ -3117,7 +3373,11 @@
           <t>software, react, front-end, technical, code, mobile, leader, health, healthcare, engineer, engineering</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>2026-03-04T00:00:29+00:00</t>
@@ -3155,7 +3415,11 @@
           <t>frontend, design, software, growth, web, management, engineer, backend, digital nomad</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>2026-03-09T09:00:04+00:00</t>
@@ -3193,7 +3457,11 @@
           <t>support, content</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>2026-03-03T18:00:40+00:00</t>
@@ -3231,7 +3499,11 @@
           <t>support, content</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>2026-03-03T18:00:21+00:00</t>
@@ -3269,7 +3541,11 @@
           <t>growth, marketing, analytics, sales, executive</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:06+00:00</t>
@@ -3349,7 +3625,11 @@
           <t>training, technical, testing, test, code, travel, microsoft, senior, legal, health</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>2026-03-10T08:00:17+00:00</t>
@@ -3387,7 +3667,11 @@
           <t>full-stack, technical, support, growth, code, cloud, management, operational, sales, engineer, engineering</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>2026-03-06T07:00:06+00:00</t>
@@ -3425,7 +3709,11 @@
           <t>python, technical, support, financial, fintech, analytics, go, health, engineering</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>2026-03-10T08:00:11+00:00</t>
@@ -3463,7 +3751,11 @@
           <t>manager, support, operations, operational</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>2026-03-10T09:00:06+00:00</t>
@@ -3501,7 +3793,11 @@
           <t>system, technical, operations, operational</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>2026-03-03T08:00:03+00:00</t>
@@ -3539,7 +3835,11 @@
           <t>system, medical, health, healthcare</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>2026-03-10T13:00:04+00:00</t>
@@ -3577,7 +3877,11 @@
           <t>manager, growth, lead, health</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>2026-03-03T16:00:20+00:00</t>
@@ -3615,7 +3919,11 @@
           <t>manager, design, architect, technical, healthcare, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>2026-03-07T00:00:47+00:00</t>
@@ -3655,7 +3963,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>18-0</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3695,7 +4003,11 @@
           <t>manager, salesforce, travel, cloud, microsoft, management, operational, analytics</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>2026-03-04T00:01:01+00:00</t>
@@ -3733,7 +4045,11 @@
           <t>saas, software, adult, c, management, senior, marketing, executive, e-commerce</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:21+00:00</t>
@@ -3771,7 +4087,11 @@
           <t>senior</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>2026-03-03T08:00:29+00:00</t>
@@ -3809,7 +4129,11 @@
           <t>manager, technical, developer, software, lead, senior, digital nomad</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>2026-03-06T08:00:15+00:00</t>
@@ -3847,7 +4171,11 @@
           <t>software, system, python, engineer, linux</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>2026-03-03T16:00:31+00:00</t>
@@ -3885,7 +4213,11 @@
           <t>manager, design, saas, crypto, bitcoin, training, technical, software, growth, financial, fintech, cloud, api, leader, management, lead, ops, operations, marketing, engineering, recruitment, executive, digital nomad</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>2026-03-06T16:00:03+00:00</t>
@@ -3923,7 +4255,11 @@
           <t>ui, ux, designer, support, education</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>2026-03-05T22:14:41+00:00</t>
@@ -3961,7 +4297,11 @@
           <t>teaching, technical, software, growth, travel, education, management, sales</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr">
         <is>
           <t>2026-03-10T16:00:04+00:00</t>
@@ -3999,7 +4339,11 @@
           <t>ios, support</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>2026-03-05T16:00:07+00:00</t>
@@ -4037,7 +4381,11 @@
           <t>analyst, consultancy, strategy, senior, analytics</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr">
         <is>
           <t>2026-03-05T23:00:28+00:00</t>
@@ -4155,7 +4503,11 @@
           <t>manager, support, management</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>2026-03-07T00:01:10+00:00</t>
@@ -4193,7 +4545,11 @@
           <t>developer, mobile, lead, android, digital nomad</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>2026-03-06T16:00:11+00:00</t>
@@ -4273,7 +4629,11 @@
           <t>security, design, support, code, management, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>2026-03-10T00:00:06+00:00</t>

--- a/output/remote_jobs.xlsx
+++ b/output/remote_jobs.xlsx
@@ -479,11 +479,7 @@
           <t>accountant, support, accounting, payroll, financial, sales, health, healthcare, non tech</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>2026-03-05T19:00:05+00:00</t>
@@ -521,11 +517,7 @@
           <t>python, game, technical, support, code, math, node, lead</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-03-09T22:00:13+00:00</t>
@@ -563,11 +555,7 @@
           <t>game, design, designer, mobile, strategy, content, senior, junior, digital nomad</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-02-28T21:00:14+00:00</t>
@@ -605,11 +593,7 @@
           <t>director, students, training, support, software</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-03-10T06:00:23+00:00</t>
@@ -647,11 +631,7 @@
           <t>architect, design, security, training, technical, growth, serverless, cloud, management, lead, junior, health, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-03-03T21:00:19+00:00</t>
@@ -689,11 +669,7 @@
           <t>design, security, training, architect, technical, support, cloud, node, management, operational, health, engineer, digital nomad</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-03-07T20:00:08+00:00</t>
@@ -731,11 +707,7 @@
           <t>design, crypto, security, support, financial, investment, api, lead, operations, operational, digital nomad</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-03-09T07:00:07+00:00</t>
@@ -773,11 +745,7 @@
           <t>analyst, crypto, training, support, financial, investment, fintech, api, operations, sales, non tech</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-03-05T11:00:07+00:00</t>
@@ -857,11 +825,7 @@
           <t>manager, technical, software, cloud, operational, engineering</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-03-07T13:00:12+00:00</t>
@@ -899,11 +863,7 @@
           <t>design, game, technical, developer, animator, animation, content, senior, digital nomad</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-03-03T21:00:06+00:00</t>
@@ -941,11 +901,7 @@
           <t>assistant, design, support, admin, content, sales, executive, full-time, digital nomad</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-03-03T07:00:02+00:00</t>
@@ -983,11 +939,7 @@
           <t>support, operational, analytics, engineering</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-03-07T00:00:35+00:00</t>
@@ -1025,11 +977,7 @@
           <t>developer, back-end, python, reliability, backend, ecommerce, e-commerce, digital nomad</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-03-06T02:00:12+00:00</t>
@@ -1109,11 +1057,7 @@
           <t>design, designer, growth, web, marketing, go, health, digital nomad</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-03-10T10:00:06+00:00</t>
@@ -1193,11 +1137,7 @@
           <t>design, system, technical, support, growth, director, lead, senior, engineer, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-03-05T23:00:14+00:00</t>
@@ -1235,11 +1175,7 @@
           <t>manager, web3, security, technical, support, travel, lead, sales, full-time</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>2026-03-05T15:00:04+00:00</t>
@@ -1277,11 +1213,7 @@
           <t>teach, technical, support, code, engineer, engineering</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>2026-03-03T17:00:17+00:00</t>
@@ -1319,11 +1251,7 @@
           <t>design, ansible, security, python, training, support, growth, code, voice, devops, education, banking, mobile, management, senior, sales, go, health, recruiting, engineer, engineering, recruitment, linux, e-commerce, digital nomad</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>2026-03-07T00:01:33+00:00</t>
@@ -1361,11 +1289,7 @@
           <t>manager, design, saas, training, support, growth, director, voice, education, banking, mobile, strategy, lead, senior, operations, marketing, sales, go, health, recruiting, recruitment, executive, digital nomad</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>2026-03-04T00:01:20+00:00</t>
@@ -1403,11 +1327,7 @@
           <t>security, software, growth, video, analytics</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>2026-03-04T00:01:42+00:00</t>
@@ -1445,11 +1365,7 @@
           <t>design, saas, technical, support, growth, strategy, management, operations, operational, digital nomad</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>2026-03-09T17:00:06+00:00</t>
@@ -1487,11 +1403,7 @@
           <t>manager, crypto, cryptocurrency, api, operational, marketing, sales</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>2026-03-03T18:00:01+00:00</t>
@@ -1529,11 +1441,7 @@
           <t>analyst, embedded, security, training, consultancy, management, senior, executive</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>2026-03-04T00:00:42+00:00</t>
@@ -1571,11 +1479,7 @@
           <t>react, software, design, jira, front-end, back-end, security, training, test, code, web, javascript, html, senior, engineer, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>2026-03-05T16:00:14+00:00</t>
@@ -1613,11 +1517,7 @@
           <t>support, software, devops, cloud, lead, content, reliability, engineer, engineering</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>2026-03-07T20:00:19+00:00</t>
@@ -1655,11 +1555,7 @@
           <t>financial, fintech, banking, senior, engineer</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>2026-03-04T08:00:21+00:00</t>
@@ -1739,11 +1635,7 @@
           <t>senior, sales, engineer</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>2026-03-10T00:01:04+00:00</t>
@@ -1781,11 +1673,7 @@
           <t>vfx, technical, lead, engineering</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>2026-03-03T22:00:12+00:00</t>
@@ -1823,11 +1711,7 @@
           <t>unity, designer, senior</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>2026-03-03T22:00:26+00:00</t>
@@ -1865,11 +1749,7 @@
           <t>growth, design, frontend, architect, technical, web, mobile, leader, lead, executive, digital nomad</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>2026-03-04T00:01:31+00:00</t>
@@ -1907,11 +1787,7 @@
           <t>manager, system, technical, software, ui, code, engineering</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>2026-03-03T00:01:09+00:00</t>
@@ -1949,11 +1825,7 @@
           <t>security, design, api, engineer, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>2026-03-09T08:00:05+00:00</t>
@@ -1991,11 +1863,7 @@
           <t>support, software, senior, engineer, engineering</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>2026-03-03T16:00:17+00:00</t>
@@ -2033,11 +1901,7 @@
           <t>support, financial, finance, fintech, strategy, operations, non tech</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>2026-03-04T00:00:08+00:00</t>
@@ -2075,11 +1939,7 @@
           <t>manager, hr, training, growth, management, lead, senior, operations, reliability</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:53+00:00</t>
@@ -2117,11 +1977,7 @@
           <t>python, django, software, design, saas, security, full-stack, technical, developer, testing, code, devops, cloud, git, postgresql, senior, operations, engineer, digital nomad</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>2026-03-09T18:00:23+00:00</t>
@@ -2159,11 +2015,7 @@
           <t>web3, cryptocurrency, voice, lead, content, operations, executive</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>2026-03-09T12:00:02+00:00</t>
@@ -2201,11 +2053,7 @@
           <t>salesforce, technical, support, administrator, management, reliability, health</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>2026-03-03T18:00:12+00:00</t>
@@ -2243,11 +2091,7 @@
           <t>system, teaching, students, technical</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>2026-03-10T00:01:14+00:00</t>
@@ -2285,11 +2129,7 @@
           <t>analyst, support, testing, leader, senior, health, healthcare, non tech</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>2026-03-10T00:00:49+00:00</t>
@@ -2327,11 +2167,7 @@
           <t>design, lead, digital nomad</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>2026-03-10T00:00:18+00:00</t>
@@ -2369,11 +2205,7 @@
           <t>accountant, saas, manager, accounting, financial, go</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>2026-03-05T20:00:07+00:00</t>
@@ -2411,11 +2243,7 @@
           <t>training, support, education, admin, management, content, non tech</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>2026-03-09T08:00:03+00:00</t>
@@ -2449,11 +2277,7 @@
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>2026-03-04T16:00:04+00:00</t>
@@ -2491,11 +2315,7 @@
           <t>analyst, support, financial, senior, analytics, health, non tech</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>2026-03-07T00:00:56+00:00</t>
@@ -2533,11 +2353,7 @@
           <t>manager, design, system, architect, technical, support, growth, voice, lead, medical, health, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>2026-03-07T00:00:08+00:00</t>
@@ -2575,11 +2391,7 @@
           <t>manager, design, saas, support, growth, financial, investment, investor, fintech, strategy, management, senior, operational, analytics, sales, reliability, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:13+00:00</t>
@@ -2617,11 +2429,7 @@
           <t>design, full-stack, architect, testing, operational, engineer, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>2026-03-10T00:00:27+00:00</t>
@@ -2659,11 +2467,7 @@
           <t>manager, saas, security, technical, growth, voice, bank, management, lead, android, sales, recruitment, executive</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>2026-03-03T08:00:20+00:00</t>
@@ -2701,11 +2505,7 @@
           <t>manager, copywriting, growth, strategy, management, content, junior</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>2026-03-06T08:00:04+00:00</t>
@@ -2743,11 +2543,7 @@
           <t>full-stack, devops, financial, fintech, cloud, senior, engineer</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>2026-03-04T00:00:17+00:00</t>
@@ -2827,11 +2623,7 @@
           <t>system, security, software, devops, operations, operational, engineer, linux</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>2026-03-04T17:00:05+00:00</t>
@@ -2869,11 +2661,7 @@
           <t>embedded, growth, analytics, engineer, engineering</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>2026-03-03T16:00:07+00:00</t>
@@ -2911,11 +2699,7 @@
           <t>design, embedded, teach, students, designer, financial, banking, senior, internship, digital nomad</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>2026-03-03T12:00:05+00:00</t>
@@ -2953,11 +2737,7 @@
           <t>system, coordinator, support, management, operational, medical, health, healthcare</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>2026-03-07T00:00:20+00:00</t>
@@ -2995,11 +2775,7 @@
           <t>training, support, leader, content, health, non tech</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>2026-03-07T00:01:21+00:00</t>
@@ -3037,11 +2813,7 @@
           <t>game, design, designer, technical, lead, content, senior, digital nomad</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>2026-02-28T21:00:04+00:00</t>
@@ -3079,11 +2851,7 @@
           <t>manager, embedded, growth, director, senior, operational, medical, health</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>2026-03-10T00:00:42+00:00</t>
@@ -3121,11 +2889,7 @@
           <t>software, design, technical, leader, senior, medical, health, engineer, digital nomad</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>2026-03-10T16:00:07+00:00</t>
@@ -3163,11 +2927,7 @@
           <t>director, training, consult, support, growth, travel, voice, financial, c, leader, strategy, management, lead, senior, marketing, sales, health, recruitment, executive, full-time</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>2026-03-10T00:00:56+00:00</t>
@@ -3205,11 +2965,7 @@
           <t>director, financial, management, sales</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>2026-03-03T08:00:13+00:00</t>
@@ -3247,11 +3003,7 @@
           <t>manager, financial, management, sales, non tech</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>2026-03-04T00:01:12+00:00</t>
@@ -3289,11 +3041,7 @@
           <t>director, saas, system, growth, leader, strategy, lead, sales, medical, health</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:31+00:00</t>
@@ -3331,11 +3079,7 @@
           <t>technical, growth, strategy, lead, senior, health, engineering</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>2026-03-09T18:00:06+00:00</t>
@@ -3373,11 +3117,7 @@
           <t>software, react, front-end, technical, code, mobile, leader, health, healthcare, engineer, engineering</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>2026-03-04T00:00:29+00:00</t>
@@ -3415,11 +3155,7 @@
           <t>frontend, design, software, growth, web, management, engineer, backend, digital nomad</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>2026-03-09T09:00:04+00:00</t>
@@ -3457,11 +3193,7 @@
           <t>support, content</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>2026-03-03T18:00:40+00:00</t>
@@ -3499,11 +3231,7 @@
           <t>support, content</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>2026-03-03T18:00:21+00:00</t>
@@ -3541,11 +3269,7 @@
           <t>growth, marketing, analytics, sales, executive</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:06+00:00</t>
@@ -3625,11 +3349,7 @@
           <t>training, technical, testing, test, code, travel, microsoft, senior, legal, health</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>2026-03-10T08:00:17+00:00</t>
@@ -3667,11 +3387,7 @@
           <t>full-stack, technical, support, growth, code, cloud, management, operational, sales, engineer, engineering</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>2026-03-06T07:00:06+00:00</t>
@@ -3709,11 +3425,7 @@
           <t>python, technical, support, financial, fintech, analytics, go, health, engineering</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>2026-03-10T08:00:11+00:00</t>
@@ -3751,11 +3463,7 @@
           <t>manager, support, operations, operational</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>2026-03-10T09:00:06+00:00</t>
@@ -3793,11 +3501,7 @@
           <t>system, technical, operations, operational</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>2026-03-03T08:00:03+00:00</t>
@@ -3835,11 +3539,7 @@
           <t>system, medical, health, healthcare</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>2026-03-10T13:00:04+00:00</t>
@@ -3877,11 +3577,7 @@
           <t>manager, growth, lead, health</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>2026-03-03T16:00:20+00:00</t>
@@ -3919,11 +3615,7 @@
           <t>manager, design, architect, technical, healthcare, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>2026-03-07T00:00:47+00:00</t>
@@ -4003,11 +3695,7 @@
           <t>manager, salesforce, travel, cloud, microsoft, management, operational, analytics</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>2026-03-04T00:01:01+00:00</t>
@@ -4045,11 +3733,7 @@
           <t>saas, software, adult, c, management, senior, marketing, executive, e-commerce</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:21+00:00</t>
@@ -4087,11 +3771,7 @@
           <t>senior</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>2026-03-03T08:00:29+00:00</t>
@@ -4129,11 +3809,7 @@
           <t>manager, technical, developer, software, lead, senior, digital nomad</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>2026-03-06T08:00:15+00:00</t>
@@ -4171,11 +3847,7 @@
           <t>software, system, python, engineer, linux</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>2026-03-03T16:00:31+00:00</t>
@@ -4213,11 +3885,7 @@
           <t>manager, design, saas, crypto, bitcoin, training, technical, software, growth, financial, fintech, cloud, api, leader, management, lead, ops, operations, marketing, engineering, recruitment, executive, digital nomad</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>2026-03-06T16:00:03+00:00</t>
@@ -4255,11 +3923,7 @@
           <t>ui, ux, designer, support, education</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>2026-03-05T22:14:41+00:00</t>
@@ -4297,11 +3961,7 @@
           <t>teaching, technical, software, growth, travel, education, management, sales</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>2026-03-10T16:00:04+00:00</t>
@@ -4339,11 +3999,7 @@
           <t>ios, support</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>2026-03-05T16:00:07+00:00</t>
@@ -4381,11 +4037,7 @@
           <t>analyst, consultancy, strategy, senior, analytics</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>2026-03-05T23:00:28+00:00</t>
@@ -4503,11 +4155,7 @@
           <t>manager, support, management</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>2026-03-07T00:01:10+00:00</t>
@@ -4545,11 +4193,7 @@
           <t>developer, mobile, lead, android, digital nomad</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>2026-03-06T16:00:11+00:00</t>
@@ -4629,11 +4273,7 @@
           <t>security, design, support, code, management, engineering, digital nomad</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>2026-03-10T00:00:06+00:00</t>

--- a/output/remote_jobs.xlsx
+++ b/output/remote_jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,33 +473,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Python Django PostgreSQL and Vue.js</t>
+          <t>Software Engineer New Grad Production Infrastructure</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GHX</t>
+          <t>Palantir Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>python, django, software, design, saas, security, full-stack, technical, developer, testing, code, devops, cloud, git, postgresql, senior, operations, engineer, digital nomad</t>
+          <t>Software, Design, Front-End, Security, Teaching, Technical, Code, Java, Cloud, Typescript, Reliability, Go, Health, Engineer, Backend</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-09T18:00:23+00:00</t>
+          <t>2026-03-13T19:00:01+00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-software-engineer-python-django-postgresql-and-vue-js-ghx-1130694</t>
+          <t>https://remoteok.com/remote-jobs/remote-software-engineer-new-grad-production-infrastructure-palantir-technologies-1130763</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -511,37 +511,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Python Backend Engineer Mission Critical</t>
+          <t>Principal VC &amp; Startup Ecosystem Lead</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amstar Curacao</t>
+          <t>Ashby</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dev, python, FastAPI, sql, linux, Pytest, Nginx, apache, javascript, react, VS Code, Remote Working, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>30000-50000</t>
-        </is>
-      </c>
+          <t>Design, Game, Founder, Manager, Edu, Strategy, Lead, Marketer, Sales, Health, Executive</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-09T10:34:28+00:00</t>
+          <t>2026-03-13T16:00:03+00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-python-backend-engineer-mission-critical-amstar-curacao-1130690</t>
+          <t>https://remoteok.com/remote-jobs/remote-principal-vc-startup-ecosystem-lead-ashby-1130762</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -553,33 +549,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Firmware Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ChowNow</t>
+          <t>Sanctuary Computer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>design, ansible, security, python, training, support, growth, code, voice, devops, education, banking, mobile, management, senior, sales, go, health, recruiting, engineer, engineering, recruitment, linux, e-commerce, digital nomad</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>Engineer, Senior, Backend, Firmware</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>$150k - $200k</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-07T00:01:33+00:00</t>
+          <t>2026-03-13T14:01:47+00:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-senior-devops-engineer-chownow-1130673</t>
+          <t>https://remoteok.com/remote-jobs/remote-senior-firmware-engineer-sanctuary-computer-1130761</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -591,36 +591,1762 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AutoDS</t>
+          <t>ELECTE S.R.L</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>developer, back-end, python, reliability, backend, ecommerce, e-commerce, digital nomad</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Engineer, JavaScript, Typescript, Python, Full-Stack, AI, Postgres</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>$30k - $50k</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-06T02:00:12+00:00</t>
+          <t>2026-03-13T12:15:25+00:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-backend-developer-autods-1130651</t>
+          <t>https://remoteok.com/remote-jobs/remote-full-stack-developer-electe-s-r-l-1130760</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Entry Level Crypto Market Specialist</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ELEMENTAL TERRA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Other, Crypto, Finance, Web3, Blockchain, Defi, Edu, Bitcoin, Ethereum, Legal</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>$50k - $70k</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-13T08:23:00+00:00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-entry-level-crypto-market-specialist-elemental-terra-1130759</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Developer Experience Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Galaxy</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Developer, Web3, Crypto, Founder, Ceo, Investment, Finance, Leader, Senior, Engineer, Engineering</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-13T08:00:37+00:00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-senior-developer-experience-engineer-galaxy-1130758</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cloud Security Architect</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Altium</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>La Jolla</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Security, Architect, Design, SaaS, System, Software, Cloud, Pcb, Engineering</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-13T08:00:11+00:00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-cloud-security-architect-altium-1130757</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Go To Market Strategist AI Trainer Freelance 8 20 hrs week</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10x Team</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Trainer, Strategist, Content, Marketing, Sales, Go, Non Tech</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-13T08:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-go-to-market-strategist-ai-trainer-freelance-8-20-hrs-week-10x-team-1130756</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Migration Specialist AI Trainer Freelance 8 20 hrs week</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10x Team</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Trainer, Technical, Content, Engineering, Part-Time</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-13T08:00:03+00:00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-migration-specialist-ai-trainer-freelance-8-20-hrs-week-10x-team-1130755</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Specialist Haitian Creole</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RWS TrainAI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Port-au-Prince</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Training, Transcription, Test, Voice, Speech</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:00:02+00:00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-ai-specialist-haitian-creole-rws-trainai-1130752</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CI&amp;T 27985 Senior AI Engineer Brazil</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CI&amp;T</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>React, System, Technical, Software, Web, API, Senior, Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-13T00:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-cit-27985-senior-ai-engineer-brazil-cit-1130751</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Client Partner Enterprise Platform Sales</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Aera Technology</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Boston, MA, USA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Support, Software, Travel, Manager, C, Leader, Management, Senior, Analytics, Sales</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-13T00:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-client-partner-enterprise-platform-sales-aera-technology-1130750</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lead 3D Environment Artist</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Eleventh Hour Games</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Upgrade to Premium to see salary</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3d, Technical, Lead, Content</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-12T22:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-lead-3d-environment-artist-eleventh-hour-games-1130749</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Principal 3D Character Artist</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Eleventh Hour Games</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3d, Technical, Senior</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-12T21:00:06+00:00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-principal-3d-character-artist-eleventh-hour-games-1130748</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior IT Project Manager</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Precision Medicine Group</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, United States</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Manager, Design, Training, Edu, Senior, Executive</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-12T20:00:06+00:00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-senior-it-project-manager-precision-medicine-group-1130747</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Technical Product Manager</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LaunchBrightly</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Technical, Developer, Engineer, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>$40k - $50k</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-12T19:16:32+00:00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-technical-product-manager-launchbrightly-1130746</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Ruby on Rails</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Versapay</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Canada (Remote)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Software, SaaS, Technical, Developer, Code, Finance, Fintech, Ruby, Rails, Senior, Ror, Engineer</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-12T17:00:02+00:00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-senior-software-engineer-ruby-on-rails-versapay-1130745</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BPM LLP AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BPM LLP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Design, Engineer</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-12T16:00:26+00:00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-bpm-llp-ai-ml-engineer-bpm-llp-1130744</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Work From Home Client Support Manager</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Global Elite Empire Consultants</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Londonderry, New Hampshire</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Manager, Support, Video, Lead, Non Tech</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-12T16:00:18+00:00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-work-from-home-client-support-manager-global-elite-empire-consultants-1130743</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Karpenter</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cast AI</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Golang, Software, Cloud, Senior, Engineer</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-12T13:00:02+00:00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-senior-software-engineer-karpenter-cast-ai-1130741</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Reporting</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cast AI</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Golang, Software, Cloud, Senior, Engineer</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-12T13:00:02+00:00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-senior-software-engineer-reporting-cast-ai-1130742</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CFO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Marathon Talent</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Cfo, Support, Software, Accounting, Financial, Finance, API, Management, Lead, Senior, Operations, Legal</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-12T08:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-cfo-marathon-talent-1130739</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pavago</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Design, C#, SaaS, System, Founder, Technical, Recruiter, Code, DevOps, Mongo, API, Strategy, Lead, Senior, Analytics, Reliability, Health, Engineer, Engineering, Linux, Backend</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-12T08:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-senior-backend-engineer-pavago-1130738</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UK Support Specialist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Substack</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Technical, Support, Content, Operations, Recruitment</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-12T08:00:03+00:00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-uk-support-specialist-substack-1130737</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Human Resources Engagement Partner</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ABBYY</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-12T00:01:28+00:00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-human-resources-engagement-partner-abbyy-1130736</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Data Platform</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Zus Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Software, Embedded, System, Ceo, Technical, Director, Code, Video, Cloud, Senior, Go, Medical, Health, Healthcare, Engineer, Engineering, Apache</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-12T00:01:18+00:00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-senior-software-engineer-data-platform-zus-health-1130735</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Corporate Associate ECVC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Scale LLP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Support, Growth, Legal</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-12T00:01:10+00:00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-corporate-associate-ecvc-scale-llp-1130734</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Recruiting Coordinator</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Zócalo Health</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>System, Coordinator, Support, Lead, Operations, Medical, Health, Healthcare, Recruiting</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-12T00:00:59+00:00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-recruiting-coordinator-zocalo-health-1130733</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Manager Revenue Accounting</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Boulevard</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Manager, Accounting, Design</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-12T00:00:49+00:00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-manager-revenue-accounting-boulevard-1130732</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Marketing Architects</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Analyst, Support, Growth, Director, Marketing, Analytics, Go, Full-Time</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-12T00:00:38+00:00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-data-analyst-marketing-architects-1130731</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Contract Data Architect</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>The Motley Fool</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Architect, Support, Financial, Investment, Strategy, Senior, Engineering</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-12T00:00:30+00:00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-contract-data-architect-the-motley-fool-1130730</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>People Operations Specialist</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Orcrist Technologies</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HR, Operations, Operational, Recruiting, Recruitment</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-12T00:00:19+00:00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-people-operations-specialist-orcrist-technologies-1130729</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Director Planning &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Temporal Technologies</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Director, Architect, Technical, Developer, Software, Growth, Finance, Lead, Operational, Analytics</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-12T00:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-director-planning-analytics-temporal-technologies-1130728</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Technical Game Designer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>That's No Moon Entertainment</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Game, Design, Designer, Technical, Animation, Content, Senior</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-11T21:00:05+00:00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-senior-technical-game-designer-thats-no-moon-entertainment-1130727</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Benefit Verification Pharmacy Technician</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Shields Health Solutions</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Operational, Medical, Educational</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-11T19:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-benefit-verification-pharmacy-technician-shields-health-solutions-1130726</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Infrastructure Manager</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Andromeda Cluster</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Manager, Training, Technical, Cloud, Strategy, Sales</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-11T16:00:03+00:00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-infrastructure-manager-andromeda-cluster-1130725</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Assistant Pricing Manager</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Restaurant Supply</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Manager, Assistant, Support, Microsoft, Operations, Excel, Ecommerce, Shopify, Non Tech</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-11T08:00:11+00:00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-assistant-pricing-manager-restaurant-supply-1130724</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AI Training for Igbo Writers</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Remotasks</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Training, Technical</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-11T06:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-ai-training-for-igbo-writers-remotasks-1130723</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Staff Threat Intelligence Researcher</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Lookout Inc</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>iOS, Security, Cloud, Mobile, Android</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-11T00:00:26+00:00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-staff-threat-intelligence-researcher-lookout-inc-1130722</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CHW Manager</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Zócalo Health</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Riverside, CA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Manager, Medical, Health, Healthcare, Non Tech</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-11T00:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-chw-manager-zocalo-health-1130721</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Lead Level Designer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Eleventh Hour Games</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Design, Designer, Lead, Engineering</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-10T22:00:45+00:00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-lead-level-designer-eleventh-hour-games-1130720</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Level Designer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Eleventh Hour Games</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Design, Game, Designer, Technical, Senior, Engineering</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-10T22:00:35+00:00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-senior-level-designer-eleventh-hour-games-1130719</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Narrative and World Lead</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Eleventh Hour Games</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Architect, Travel, Strategy, Lead</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-10T22:00:25+00:00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-narrative-and-world-lead-eleventh-hour-games-1130718</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Procurement Specialist Hardware</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Blueprint</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Support, Strategy, Operations</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-10T22:00:12+00:00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-procurement-specialist-hardware-blueprint-1130717</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Lead Animator</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Eleventh Hour Games</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Design, Game, Animator, Animation, Lead</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-10T21:00:17+00:00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-lead-animator-eleventh-hour-games-1130715</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Omada Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Software, Design, Technical, Leader, Senior, Medical, Health, Engineer</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-10T16:00:07+00:00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-senior-software-engineer-omada-health-1130714</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Territory Sales Representative Green Grass Southeast</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Trackman A/S</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Probably worldwide</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Teaching, Technical, Software, Growth, Travel, Edu, Management, Sales</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-10T16:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-territory-sales-representative-green-grass-southeast-trackman-a-s-1130713</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Stellar AI</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>🇪🇺 Europe</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Developer, Train</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>$90k - $130k</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-05T00:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-senior-software-engineer-stellar-ai-1128869</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Frontend Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Engineer, Developer, JavaScript, React, Typescript, GraphQL, AI, Front End</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>$180k - $180k</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-03T17:34:49+00:00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-jobs/remote-senior-frontend-engineer-level-1130614</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>RemoteOK</t>
         </is>
